--- a/shablon_import.xlsx
+++ b/shablon_import.xlsx
@@ -1,17 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FFD4D3-799F-41D4-A712-9AC03A09C7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-27990" yWindow="0" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Исходные данные" state="visible" r:id="rId4"/>
+    <sheet name="Исходные данные" sheetId="1" r:id="rId1"/>
+    <sheet name="корпус 1.3" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="55">
   <si>
     <t>Параметр</t>
   </si>
@@ -25,12 +43,6 @@
     <t/>
   </si>
   <si>
-    <t>Система отопления</t>
-  </si>
-  <si>
-    <t>Разводка</t>
-  </si>
-  <si>
     <t>Температурный график</t>
   </si>
   <si>
@@ -55,71 +67,175 @@
     <t>Толщина изоляции, мм</t>
   </si>
   <si>
-    <t>Этажи</t>
-  </si>
-  <si>
-    <t>Квартир (всего)</t>
-  </si>
-  <si>
     <t>Квартир на этаже</t>
   </si>
   <si>
-    <t>Пар стояков</t>
-  </si>
-  <si>
-    <t>Выходов гребёнок</t>
-  </si>
-  <si>
     <t>Зон отопления</t>
   </si>
   <si>
-    <t>Границы зон</t>
-  </si>
-  <si>
-    <t>Длина коридора, м</t>
-  </si>
-  <si>
-    <t>Комнат на квартиру</t>
-  </si>
-  <si>
     <t>Тип разводки PEX</t>
   </si>
   <si>
     <t>Лучевая</t>
   </si>
   <si>
-    <t>Ширина 1700 мм</t>
-  </si>
-  <si>
-    <t>Ширина 1850 мм</t>
-  </si>
-  <si>
-    <t>Ширина 1200 мм</t>
-  </si>
-  <si>
-    <t>Ширина 840 мм</t>
-  </si>
-  <si>
-    <t>Ширина 3040 мм</t>
-  </si>
-  <si>
-    <t>Ширина 2000 мм</t>
+    <t>ВГГ-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Секция </t>
+  </si>
+  <si>
+    <t>КОРПУС 1.1</t>
+  </si>
+  <si>
+    <t>КОРПУС 1.2</t>
+  </si>
+  <si>
+    <t>Кол-во</t>
+  </si>
+  <si>
+    <t>попутная</t>
+  </si>
+  <si>
+    <t>Количество квартир</t>
+  </si>
+  <si>
+    <t>Однокомнатные</t>
+  </si>
+  <si>
+    <t>Двухкомнатные</t>
+  </si>
+  <si>
+    <t>Трехкомнатные</t>
+  </si>
+  <si>
+    <t>Четырехкомнатные</t>
+  </si>
+  <si>
+    <t>ХВС</t>
+  </si>
+  <si>
+    <t>1 зона м</t>
+  </si>
+  <si>
+    <t>кол-во стояков</t>
+  </si>
+  <si>
+    <t>2 зона м</t>
+  </si>
+  <si>
+    <t>всего</t>
+  </si>
+  <si>
+    <t>труба Ду 50</t>
+  </si>
+  <si>
+    <t>этаж</t>
+  </si>
+  <si>
+    <t>кол-во выходов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Воздухоотводчик </t>
+  </si>
+  <si>
+    <t>квартир</t>
+  </si>
+  <si>
+    <t>разводка PP-R Ду 15</t>
+  </si>
+  <si>
+    <t>Проверка по кол-ву квартир</t>
+  </si>
+  <si>
+    <t>Проверка по кол-ву этажей</t>
+  </si>
+  <si>
+    <t>Этажи/кол-во квартир</t>
+  </si>
+  <si>
+    <t>Кол-во этажей корпуса</t>
+  </si>
+  <si>
+    <t>Границы зон (Этаж)</t>
+  </si>
+  <si>
+    <t>Символ 36 корп</t>
+  </si>
+  <si>
+    <t>Секция 1</t>
+  </si>
+  <si>
+    <t>Секция 2</t>
+  </si>
+  <si>
+    <t>Секция 3</t>
+  </si>
+  <si>
+    <t>Секция 4</t>
+  </si>
+  <si>
+    <t>Секция 5</t>
+  </si>
+  <si>
+    <t>Итог</t>
+  </si>
+  <si>
+    <t>ВГГ-5 КОРПУС 1.1+1.2</t>
+  </si>
+  <si>
+    <t>ВГГ-5 КОРПУС 1.3</t>
+  </si>
+  <si>
+    <t>КОРПУС 1.3 Итог</t>
+  </si>
+  <si>
+    <t>Квартир на этаже(отводов коллекторов\количество данных этажей</t>
+  </si>
+  <si>
+    <t>ширина простенка окна мм/кол-во</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -147,20 +263,29 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{2FD0EF42-99CB-4947-8403-A6AAA4FE7AC1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -173,6 +298,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6843983" cy="3216071"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{315B897E-16FC-47A6-B347-6B33489734A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9349740" y="213360"/>
+          <a:ext cx="6843983" cy="3216071"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>511628</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>87085</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6498314" cy="4086779"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1F1E84D-E7BD-4DB2-9735-9C33E76B29DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9274628" y="3706585"/>
+          <a:ext cx="6498314" cy="4086779"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,15 +704,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M117"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -512,216 +722,2647 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <f>1021</f>
+        <v>1021</v>
+      </c>
+      <c r="E6">
+        <v>801</v>
+      </c>
+      <c r="K6">
+        <f>1901+996.72</f>
+        <v>2897.7200000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <f>SUM(B100:B214)</f>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f>SUM(C100:C214)</f>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f>SUM(D100:D214)</f>
+        <v>220</v>
+      </c>
+      <c r="E7">
+        <f>SUM(E100:E214)</f>
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <f>SUM(F100:F214)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>3000</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>3000</v>
+      </c>
+      <c r="E10">
+        <v>3000</v>
+      </c>
+      <c r="F10">
+        <v>3300</v>
+      </c>
+      <c r="G10">
+        <v>3300</v>
+      </c>
+      <c r="H10">
+        <v>3300</v>
+      </c>
+      <c r="I10">
+        <v>3300</v>
+      </c>
+      <c r="J10">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="E11">
         <v>13</v>
       </c>
-      <c r="B11">
+      <c r="F11">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>25</v>
+      </c>
+      <c r="H11">
+        <v>25</v>
+      </c>
+      <c r="I11">
+        <v>25</v>
+      </c>
+      <c r="J11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>25</v>
+      </c>
+      <c r="F12">
+        <v>23</v>
+      </c>
+      <c r="G12">
+        <v>26</v>
+      </c>
+      <c r="H12">
+        <v>27</v>
+      </c>
+      <c r="I12">
+        <v>22</v>
+      </c>
+      <c r="J12">
+        <v>17</v>
+      </c>
+      <c r="M12">
+        <f>SUM(F12:L12)</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>82</v>
+      </c>
+      <c r="C13">
+        <v>77</v>
+      </c>
+      <c r="D13">
+        <f>B13+C13</f>
+        <v>159</v>
+      </c>
+      <c r="E13">
+        <v>270</v>
+      </c>
+      <c r="K13">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <v>60</v>
+      </c>
+      <c r="C14">
+        <v>38</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ref="D14:D17" si="0">B14+C14</f>
+        <v>98</v>
+      </c>
+      <c r="E14">
+        <v>128</v>
+      </c>
+      <c r="M14">
+        <f>K13/M12</f>
+        <v>6.5043478260869563</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>39</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="E15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E16">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+      <c r="H19">
+        <v>7</v>
+      </c>
+      <c r="I19">
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="E20">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20">
+        <v>7</v>
+      </c>
+      <c r="I20">
+        <v>7</v>
+      </c>
+      <c r="J20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <v>7</v>
+      </c>
+      <c r="H21">
+        <v>7</v>
+      </c>
+      <c r="I21">
+        <v>7</v>
+      </c>
+      <c r="J21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="E22">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <v>7</v>
+      </c>
+      <c r="H22">
+        <v>7</v>
+      </c>
+      <c r="I22">
+        <v>7</v>
+      </c>
+      <c r="J22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>6</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23">
+        <v>7</v>
+      </c>
+      <c r="H23">
+        <v>7</v>
+      </c>
+      <c r="I23">
+        <v>7</v>
+      </c>
+      <c r="J23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>7</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>7</v>
+      </c>
+      <c r="G24">
+        <v>7</v>
+      </c>
+      <c r="H24">
+        <v>7</v>
+      </c>
+      <c r="I24">
+        <v>7</v>
+      </c>
+      <c r="J24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>8</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="E25">
+        <v>11</v>
+      </c>
+      <c r="F25">
+        <v>7</v>
+      </c>
+      <c r="G25">
+        <v>7</v>
+      </c>
+      <c r="H25">
+        <v>7</v>
+      </c>
+      <c r="I25">
+        <v>7</v>
+      </c>
+      <c r="J25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>9</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>7</v>
+      </c>
+      <c r="H26">
+        <v>7</v>
+      </c>
+      <c r="I26">
+        <v>7</v>
+      </c>
+      <c r="J26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>10</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>11</v>
+      </c>
+      <c r="F27">
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
+      </c>
+      <c r="H27">
+        <v>7</v>
+      </c>
+      <c r="I27">
+        <v>7</v>
+      </c>
+      <c r="J27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>11</v>
+      </c>
+      <c r="F28">
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <v>7</v>
+      </c>
+      <c r="H28">
+        <v>7</v>
+      </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
+      <c r="J28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>12</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>11</v>
+      </c>
+      <c r="F29">
+        <v>7</v>
+      </c>
+      <c r="G29">
+        <v>7</v>
+      </c>
+      <c r="H29">
+        <v>7</v>
+      </c>
+      <c r="I29">
+        <v>7</v>
+      </c>
+      <c r="J29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>11</v>
+      </c>
+      <c r="F30">
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <v>7</v>
+      </c>
+      <c r="H30">
+        <v>7</v>
+      </c>
+      <c r="I30">
+        <v>7</v>
+      </c>
+      <c r="J30">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>11</v>
+      </c>
+      <c r="F31">
+        <v>7</v>
+      </c>
+      <c r="G31">
+        <v>7</v>
+      </c>
+      <c r="H31">
+        <v>7</v>
+      </c>
+      <c r="I31">
+        <v>7</v>
+      </c>
+      <c r="J31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>15</v>
+      </c>
+      <c r="B32">
+        <v>5</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="E32">
+        <v>11</v>
+      </c>
+      <c r="F32">
+        <v>7</v>
+      </c>
+      <c r="G32">
+        <v>7</v>
+      </c>
+      <c r="H32">
+        <v>7</v>
+      </c>
+      <c r="I32">
+        <v>7</v>
+      </c>
+      <c r="J32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>16</v>
+      </c>
+      <c r="B33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>11</v>
+      </c>
+      <c r="F33">
+        <v>7</v>
+      </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+      <c r="H33">
+        <v>7</v>
+      </c>
+      <c r="I33">
+        <v>7</v>
+      </c>
+      <c r="J33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+      <c r="E34">
+        <v>11</v>
+      </c>
+      <c r="F34">
+        <v>7</v>
+      </c>
+      <c r="G34">
+        <v>7</v>
+      </c>
+      <c r="H34">
+        <v>7</v>
+      </c>
+      <c r="I34">
+        <v>7</v>
+      </c>
+      <c r="J34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>18</v>
+      </c>
+      <c r="E35">
+        <v>11</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>7</v>
+      </c>
+      <c r="H35">
+        <v>7</v>
+      </c>
+      <c r="I35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>19</v>
+      </c>
+      <c r="E36">
+        <v>11</v>
+      </c>
+      <c r="F36">
+        <v>7</v>
+      </c>
+      <c r="G36">
+        <v>7</v>
+      </c>
+      <c r="H36">
+        <v>7</v>
+      </c>
+      <c r="I36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>20</v>
+      </c>
+      <c r="E37">
+        <v>11</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37">
+        <v>6</v>
+      </c>
+      <c r="H37">
+        <v>6</v>
+      </c>
+      <c r="I37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>21</v>
+      </c>
+      <c r="E38">
+        <v>11</v>
+      </c>
+      <c r="F38">
+        <v>6</v>
+      </c>
+      <c r="G38">
+        <v>6</v>
+      </c>
+      <c r="H38">
+        <v>6</v>
+      </c>
+      <c r="I38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>22</v>
+      </c>
+      <c r="E39">
+        <v>11</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+      <c r="G39">
+        <v>6</v>
+      </c>
+      <c r="H39">
+        <v>6</v>
+      </c>
+      <c r="I39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>23</v>
+      </c>
+      <c r="E40">
+        <v>11</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40">
+        <v>6</v>
+      </c>
+      <c r="H40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>24</v>
+      </c>
+      <c r="E41">
+        <v>11</v>
+      </c>
+      <c r="G41">
+        <v>6</v>
+      </c>
+      <c r="H41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>25</v>
+      </c>
+      <c r="E42">
+        <v>11</v>
+      </c>
+      <c r="G42">
+        <v>6</v>
+      </c>
+      <c r="H42">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>26</v>
+      </c>
+      <c r="G43">
+        <v>6</v>
+      </c>
+      <c r="H43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>27</v>
+      </c>
+      <c r="H44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2</v>
+      </c>
+      <c r="B76">
+        <f t="shared" ref="B76:D87" si="1">COUNTIF(B$19:B$73,$A76)</f>
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <f>COUNTIF(E$19:E$73,$A76)</f>
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <f t="shared" ref="F76:M76" si="2">COUNTIF(F$19:F$73,$A76)</f>
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B77">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <f t="shared" ref="E77:M87" si="3">COUNTIF(E$19:E$73,$A77)</f>
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>4</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>5</v>
+      </c>
+      <c r="B79">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>7</v>
+      </c>
+      <c r="B81">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>8</v>
+      </c>
+      <c r="B82">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>9</v>
+      </c>
+      <c r="B83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>10</v>
+      </c>
+      <c r="B84">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>11</v>
+      </c>
+      <c r="B85">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>12</v>
+      </c>
+      <c r="B86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>13</v>
+      </c>
+      <c r="B87">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>38</v>
+      </c>
+      <c r="B88">
+        <f>B76*$A$76+B77*$A$77+B78*$A$78+B79*$A$79+B80*$A$80+B81*$A$81+B82*$A$82+B83*$A$83+B84*$A$84+B85*$A$85-B13</f>
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <f t="shared" ref="C88" si="4">C76*$A$76+C77*$A$77+C78*$A$78+C79*$A$79+C80*$A$80+C81*$A$81+C82*$A$82+C83*$A$83+C84*$A$84+C85*$A$85-C13</f>
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <f>D76*$A$76+D77*$A$77+D78*$A$78+D79*$A$79+D80*$A$80+D81*$A$81+D82*$A$82+D83*$A$83+D84*$A$84+D85*$A$85-D13</f>
+        <v>-159</v>
+      </c>
+      <c r="E88">
+        <f>E76*$A$76+E77*$A$77+E78*$A$78+E79*$A$79+E80*$A$80+E81*$A$81+E82*$A$82+E83*$A$83+E84*$A$84+E85*$A$85+E86*$A$86+E87*$A$87-E13</f>
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <f t="shared" ref="F88:M88" si="5">F76*$A$76+F77*$A$77+F78*$A$78+F79*$A$79+F80*$A$80+F81*$A$81+F82*$A$82+F83*$A$83+F84*$A$84+F85*$A$85+F86*$A$86+F87*$A$87-F13</f>
+        <v>150</v>
+      </c>
+      <c r="G88">
+        <f t="shared" si="5"/>
+        <v>168</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="5"/>
+        <v>174</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="5"/>
+        <v>147</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="5"/>
+        <v>109</v>
+      </c>
+      <c r="K88">
+        <f>K76*$A$76+K77*$A$77+K78*$A$78+K79*$A$79+K80*$A$80+K81*$A$81+K82*$A$82+K83*$A$83+K84*$A$84+K85*$A$85+K86*$A$86+K87*$A$87-K13+1</f>
+        <v>-747</v>
+      </c>
+      <c r="L88">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89">
+        <f>SUM(B76:B85)-B12+1</f>
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <f t="shared" ref="C89:D89" si="6">SUM(C76:C85)-C12+1</f>
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <f>SUM(E76:E87)-E12+1</f>
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <f t="shared" ref="F89:M89" si="7">SUM(F76:F87)-F12+1</f>
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="L89">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="M89">
+        <f t="shared" si="7"/>
+        <v>-114</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>13</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="F92">
+        <v>2</v>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+      <c r="H92">
+        <v>2</v>
+      </c>
+      <c r="I92">
+        <v>2</v>
+      </c>
+      <c r="J92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>42</v>
+      </c>
+      <c r="B93" t="s">
+        <v>3</v>
+      </c>
+      <c r="E93">
+        <v>16</v>
+      </c>
+      <c r="F93">
         <v>15</v>
       </c>
-      <c r="B13" t="s">
+      <c r="G93">
+        <v>15</v>
+      </c>
+      <c r="H93">
+        <v>15</v>
+      </c>
+      <c r="I93">
+        <v>15</v>
+      </c>
+      <c r="J93">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" t="s">
+        <v>21</v>
+      </c>
+      <c r="G94" t="s">
+        <v>21</v>
+      </c>
+      <c r="H94" t="s">
+        <v>21</v>
+      </c>
+      <c r="I94" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>4</v>
+      </c>
+      <c r="B97" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" t="s">
+        <v>5</v>
+      </c>
+      <c r="E97" t="s">
+        <v>5</v>
+      </c>
+      <c r="F97" t="s">
+        <v>5</v>
+      </c>
+      <c r="G97" t="s">
+        <v>5</v>
+      </c>
+      <c r="H97" t="s">
+        <v>5</v>
+      </c>
+      <c r="I97" t="s">
+        <v>5</v>
+      </c>
+      <c r="J97" t="s">
+        <v>5</v>
+      </c>
+      <c r="K97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98">
+        <v>800</v>
+      </c>
+      <c r="C98">
+        <v>800</v>
+      </c>
+      <c r="D98">
+        <v>800</v>
+      </c>
+      <c r="E98">
+        <v>800</v>
+      </c>
+      <c r="F98">
+        <v>600</v>
+      </c>
+      <c r="G98">
+        <v>600</v>
+      </c>
+      <c r="H98">
+        <v>600</v>
+      </c>
+      <c r="I98">
+        <v>600</v>
+      </c>
+      <c r="J98">
+        <v>600</v>
+      </c>
+      <c r="K98">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>54</v>
+      </c>
+      <c r="B99" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1700</v>
+      </c>
+      <c r="D100">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1850</v>
+      </c>
+      <c r="D101">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1200</v>
+      </c>
+      <c r="D102">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>840</v>
+      </c>
+      <c r="D103">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>3040</v>
+      </c>
+      <c r="D104">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>2000</v>
+      </c>
+      <c r="D105">
+        <v>50</v>
+      </c>
+      <c r="E105">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>1200</v>
+      </c>
+      <c r="B106" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="K106">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>1200</v>
+      </c>
+      <c r="K107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>1500</v>
+      </c>
+      <c r="K108">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>1500</v>
+      </c>
+      <c r="K109">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1800</v>
+      </c>
+      <c r="K110">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1800</v>
+      </c>
+      <c r="K111">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>2100</v>
+      </c>
+      <c r="K112">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>2100</v>
+      </c>
+      <c r="K113">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>2400</v>
+      </c>
+      <c r="K114">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>2400</v>
+      </c>
+      <c r="K115">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>900</v>
+      </c>
+      <c r="K116">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>900</v>
+      </c>
+      <c r="K117">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A41F6CD-7387-4A33-BD56-A033B2E54AE7}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="4"/>
+    <col min="3" max="3" width="14.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="4"/>
+    <col min="5" max="5" width="14.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="9.140625" style="4"/>
+    <col min="10" max="11" width="14.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="4">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4">
+        <v>86</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2</v>
+      </c>
+      <c r="F2" s="4">
+        <f>(B2*C2)+(D2*E2)</f>
+        <v>264</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H3" s="4">
+        <f>J3+K3</f>
+        <v>12</v>
+      </c>
+      <c r="I3" s="4">
+        <v>2</v>
+      </c>
+      <c r="J3" s="4">
+        <v>6</v>
+      </c>
+      <c r="K3" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="4">
+        <v>4</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" ref="H4:H26" si="0">J4+K4</f>
+        <v>12</v>
+      </c>
+      <c r="I4" s="4">
+        <v>3</v>
+      </c>
+      <c r="J4" s="4">
+        <v>6</v>
+      </c>
+      <c r="K4" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H5" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I5" s="4">
+        <v>4</v>
+      </c>
+      <c r="J5" s="4">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="4">
+        <v>429</v>
+      </c>
+      <c r="C6" s="4">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4">
+        <f>B6/C6</f>
+        <v>17.875</v>
+      </c>
+      <c r="F6" s="4">
+        <v>18</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I6" s="4">
+        <v>5</v>
+      </c>
+      <c r="J6" s="4">
+        <v>6</v>
+      </c>
+      <c r="K6" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H7" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I7" s="4">
+        <v>6</v>
+      </c>
+      <c r="J7" s="4">
+        <v>6</v>
+      </c>
+      <c r="K7" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="4">
+        <f>16*25</f>
+        <v>400</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I8" s="4">
+        <v>7</v>
+      </c>
+      <c r="J8" s="4">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <f>1.5*B6</f>
+        <v>643.5</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I9" s="4">
+        <v>8</v>
+      </c>
+      <c r="J9" s="4">
+        <v>5</v>
+      </c>
+      <c r="K9" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <f>SUM(B8:B9)</f>
+        <v>1043.5</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="4">
+        <f>B10*C10</f>
+        <v>208.70000000000002</v>
+      </c>
+      <c r="E10" s="3">
+        <f>B10+D10</f>
+        <v>1252.2</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I10" s="4">
+        <v>9</v>
+      </c>
+      <c r="J10" s="4">
+        <v>5</v>
+      </c>
+      <c r="K10" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H11" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I11" s="4">
+        <v>10</v>
+      </c>
+      <c r="J11" s="4">
+        <v>5</v>
+      </c>
+      <c r="K11" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H12" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I12" s="4">
+        <v>11</v>
+      </c>
+      <c r="J12" s="4">
+        <v>5</v>
+      </c>
+      <c r="K12" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H13" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I13" s="4">
+        <v>12</v>
+      </c>
+      <c r="J13" s="4">
+        <v>5</v>
+      </c>
+      <c r="K13" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H14" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I14" s="4">
+        <v>13</v>
+      </c>
+      <c r="J14" s="4">
+        <v>5</v>
+      </c>
+      <c r="K14" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H15" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I15" s="4">
+        <v>14</v>
+      </c>
+      <c r="J15" s="4">
+        <v>5</v>
+      </c>
+      <c r="K15" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C16" s="4">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I16" s="4">
+        <v>15</v>
+      </c>
+      <c r="J16" s="4">
+        <v>5</v>
+      </c>
+      <c r="K16" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H17" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I17" s="4">
         <v>16</v>
       </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="J17" s="4">
+        <v>5</v>
+      </c>
+      <c r="K17" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H18" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I18" s="4">
         <v>17</v>
       </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="J18" s="4">
+        <v>5</v>
+      </c>
+      <c r="K18" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H19" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I19" s="4">
         <v>18</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="J19" s="4">
+        <v>5</v>
+      </c>
+      <c r="K19" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H20" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I20" s="4">
         <v>19</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="J20" s="4">
+        <v>5</v>
+      </c>
+      <c r="K20" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H21" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I21" s="4">
         <v>20</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="J21" s="4">
+        <v>5</v>
+      </c>
+      <c r="K21" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H22" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I22" s="4">
         <v>21</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="J22" s="4">
+        <v>5</v>
+      </c>
+      <c r="K22" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H23" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I23" s="4">
         <v>22</v>
       </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="J23" s="4">
+        <v>5</v>
+      </c>
+      <c r="K23" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H24" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I24" s="4">
         <v>23</v>
       </c>
-      <c r="B21" t="s">
+      <c r="J24" s="4">
+        <v>5</v>
+      </c>
+      <c r="K24" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H25" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I25" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="J25" s="4">
+        <v>5</v>
+      </c>
+      <c r="K25" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H26" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I26" s="4">
         <v>25</v>
       </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" t="s">
-        <v>3</v>
+      <c r="J26" s="4">
+        <v>5</v>
+      </c>
+      <c r="K26" s="4">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>